--- a/notes/曾卉招行贷款利息帮扶记录.xlsx
+++ b/notes/曾卉招行贷款利息帮扶记录.xlsx
@@ -25,72 +25,7 @@
     <t xml:space="preserve">曾卉招行贷款利息帮扶记录</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">约定（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF666666"/>
-        <rFont val="等线"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026-07</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">，口头）：招商银行 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF666666"/>
-        <rFont val="等线"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">30 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">万元贷款，每月利息（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF666666"/>
-        <rFont val="等线"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1,000 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">多元）由我们代付，本金由曾卉自行偿还。待补充：本金还款计划、帮扶期限或总额上限。</t>
-    </r>
+    <t xml:space="preserve">约定（2026-07，口头）：招商银行 30 万元贷款（期限 3 年，2025 下半年借出，约 2028 下半年到期），每月利息（1,000 多元）由我们代付，本金由曾卉自行偿还。待确认：还款方式（先息后本或等额本息）；待补充：她的本金还款计划。</t>
   </si>
   <si>
     <t xml:space="preserve">填写说明：每次转账后在下表记一行（黄色为示例行，首次填写时请覆盖）；「招行本金余额」在与曾卉对账时更新；「累计已代付」自动计算。</t>
@@ -126,7 +61,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.00"/>
     <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -154,18 +89,13 @@
       <sz val="14"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF666666"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF666666"/>
-      <name val="等线"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
@@ -173,6 +103,7 @@
       <sz val="11"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -191,6 +122,7 @@
       <sz val="11"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -262,12 +194,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -275,43 +211,43 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -570,247 +506,247 @@
   <dimension ref="A1:E30"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="42"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="4" t="n">
+      <c r="B4" s="4"/>
+      <c r="C4" s="5" t="n">
         <f aca="false">SUM(C6:C205)</f>
         <v>1050</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="n">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="7" t="n">
+      <c r="B6" s="8" t="n">
         <v>46244</v>
       </c>
-      <c r="C6" s="8" t="n">
+      <c r="C6" s="9" t="n">
         <v>1050</v>
       </c>
-      <c r="D6" s="8" t="n">
+      <c r="D6" s="9" t="n">
         <v>300000</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="10" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10"/>
-      <c r="B7" s="11"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="10"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="10"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="10"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="10"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="10"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="10"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="10"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="10"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="10"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="10"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="10"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="10"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="10"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="10"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="10"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="10"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="10"/>
-      <c r="B21" s="11"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="10"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="10"/>
-      <c r="B22" s="11"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="10"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="10"/>
-      <c r="B23" s="11"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="10"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="10"/>
-      <c r="B24" s="11"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="10"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="10"/>
-      <c r="B25" s="11"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="10"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="10"/>
-      <c r="B26" s="11"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="10"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="10"/>
-      <c r="B27" s="11"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="10"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="10"/>
-      <c r="B28" s="11"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="10"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="10"/>
-      <c r="B29" s="11"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="10"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="10"/>
-      <c r="B30" s="11"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="10"/>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="11"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="11"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="11"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="11"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="11"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="11"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="11"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="11"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="11"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="11"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="11"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="11"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="11"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="11"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="11"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="11"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="11"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="11"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="11"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="11"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="11"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="11"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="11"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="11"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="11"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="11"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="11"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="11"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="11"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="11"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="11"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="11"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="11"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="11"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="11"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="11"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="11"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="11"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="11"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="11"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="11"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="11"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="11"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="11"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="11"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="11"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="11"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="3">
